--- a/artfynd/A 16735-2026 artfynd.xlsx
+++ b/artfynd/A 16735-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132614866</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132614842</v>
+        <v>132614841</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515511</v>
+        <v>515525</v>
       </c>
       <c r="R3" t="n">
-        <v>7099483</v>
+        <v>7099520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132614870</v>
+        <v>132614842</v>
       </c>
       <c r="B4" t="n">
-        <v>80438</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515623</v>
+        <v>515511</v>
       </c>
       <c r="R4" t="n">
-        <v>7099680</v>
+        <v>7099483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132614871</v>
+        <v>132698147</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515503</v>
+        <v>515581</v>
       </c>
       <c r="R5" t="n">
-        <v>7099481</v>
+        <v>7099538</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,69 +1046,99 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en stående lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132614841</v>
+        <v>132698188</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515525</v>
+        <v>515517</v>
       </c>
       <c r="R6" t="n">
-        <v>7099520</v>
+        <v>7099441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,28 +1179,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132698177</v>
+        <v>132698190</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,30 +1214,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1202,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515515</v>
+        <v>515571</v>
       </c>
       <c r="R7" t="n">
-        <v>7099482</v>
+        <v>7099477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,26 +1293,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1290,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132698158</v>
+        <v>132698191</v>
       </c>
       <c r="B8" t="n">
-        <v>80467</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,30 +1321,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1332,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515534</v>
+        <v>515453</v>
       </c>
       <c r="R8" t="n">
-        <v>7099502</v>
+        <v>7099444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,21 +1400,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1415,14 +1417,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132698206</v>
+        <v>132698200</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1453,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515629</v>
+        <v>515473</v>
       </c>
       <c r="R9" t="n">
-        <v>7099630</v>
+        <v>7099399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,65 +1538,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132698183</v>
+        <v>132698206</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515624</v>
+        <v>515629</v>
       </c>
       <c r="R10" t="n">
-        <v>7099623</v>
+        <v>7099630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,12 +1620,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1658,38 +1659,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132698160</v>
+        <v>132698207</v>
       </c>
       <c r="B11" t="n">
-        <v>97995</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515607</v>
+        <v>515553</v>
       </c>
       <c r="R11" t="n">
-        <v>7099550</v>
+        <v>7099497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,6 +1748,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1765,65 +1780,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132698186</v>
+        <v>132698208</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515479</v>
+        <v>515510</v>
       </c>
       <c r="R12" t="n">
-        <v>7099453</v>
+        <v>7099459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,18 +1856,44 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1887,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132698147</v>
+        <v>132614869</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,41 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515581</v>
+        <v>515670</v>
       </c>
       <c r="R13" t="n">
-        <v>7099538</v>
+        <v>7099669</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,60 +1984,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en stående lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132698207</v>
+        <v>132614870</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,37 +2019,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515553</v>
+        <v>515623</v>
       </c>
       <c r="R14" t="n">
-        <v>7099497</v>
+        <v>7099680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,49 +2087,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132698196</v>
+        <v>132614871</v>
       </c>
       <c r="B15" t="n">
-        <v>57136</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,46 +2116,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515538</v>
+        <v>515503</v>
       </c>
       <c r="R15" t="n">
-        <v>7099497</v>
+        <v>7099481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,11 +2178,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färsk spillning i lämplig livsmiljö för järpe.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2236,36 +2186,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Flerskiktad granskog med inslag av björk och sälg.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132698169</v>
+        <v>132698162</v>
       </c>
       <c r="B16" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2292,11 +2232,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2304,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515625</v>
+        <v>515481</v>
       </c>
       <c r="R16" t="n">
-        <v>7099628</v>
+        <v>7099415</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,14 +2303,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2392,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132698174</v>
+        <v>132698163</v>
       </c>
       <c r="B17" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515517</v>
+        <v>515477</v>
       </c>
       <c r="R17" t="n">
-        <v>7099481</v>
+        <v>7099420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132614850</v>
+        <v>132698169</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,34 +2455,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515444</v>
+        <v>515625</v>
       </c>
       <c r="R18" t="n">
-        <v>7099428</v>
+        <v>7099628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,39 +2524,60 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132614848</v>
+        <v>132698170</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,34 +2585,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515572</v>
+        <v>515630</v>
       </c>
       <c r="R19" t="n">
-        <v>7099501</v>
+        <v>7099540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,39 +2650,55 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132614849</v>
+        <v>132698172</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2706,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515499</v>
+        <v>515588</v>
       </c>
       <c r="R20" t="n">
-        <v>7099470</v>
+        <v>7099511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,7 +2777,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt med lunglav på en död upplyft sälglåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,28 +2786,54 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132698150</v>
+        <v>132698173</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,31 +2841,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2862,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515444</v>
+        <v>515589</v>
       </c>
       <c r="R21" t="n">
-        <v>7099420</v>
+        <v>7099496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,17 +2906,13 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran. På/kring fyndplatsen finns stående död ved i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett. Även gott om vindfälld gran här.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2921,22 +2923,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2951,6 +2948,2257 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132698174</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>515517</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7099481</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132698157</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>515645</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7099540</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132698158</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>515534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7099502</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132698175</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>515642</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7099645</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132698176</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>515585</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7099498</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132698177</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>515515</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7099482</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132614843</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>515448</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7099409</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132614848</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>515572</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7099501</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132614849</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>515499</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7099470</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132614850</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>515444</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7099428</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132698150</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>515444</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7099420</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran. På/kring fyndplatsen finns stående död ved i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett. Även gott om vindfälld gran här.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132698196</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>515538</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7099497</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färsk spillning i lämplig livsmiljö för järpe.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Flerskiktad granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132698183</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>515624</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7099623</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132698186</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>515479</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7099453</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132698179</v>
+      </c>
+      <c r="B36" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>515644</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7099629</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132698180</v>
+      </c>
+      <c r="B37" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>515465</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7099425</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132698195</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>515658</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7099621</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132698145</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>515573</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7099479</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Flera frökapslar och gröna blad på fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132698160</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>515607</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7099550</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16735-2026 artfynd.xlsx
+++ b/artfynd/A 16735-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614866</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698188</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698190</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698191</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698206</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698207</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2005,6 +2065,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614869</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614870</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2199,6 +2269,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614871</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2320,6 +2395,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698162</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2441,6 +2521,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698163</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698169</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2692,6 +2782,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698170</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2827,6 +2922,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698172</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2948,6 +3048,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698173</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3069,6 +3174,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698174</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3204,6 +3314,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698157</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3329,6 +3444,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698158</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3455,6 +3575,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698175</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3585,6 +3710,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698176</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3715,6 +3845,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698177</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3817,6 +3952,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614843</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3919,6 +4059,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614848</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4021,6 +4166,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614849</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4123,6 +4273,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614850</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4258,6 +4413,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698150</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4382,6 +4542,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698196</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4504,6 +4669,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698183</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4626,6 +4796,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698186</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4737,6 +4912,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698179</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4848,6 +5028,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698180</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4976,6 +5161,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698195</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5092,6 +5282,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698145</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5199,8 +5394,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698160</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>